--- a/ゲーム科1年/01_後期/ゲームプログラミングⅢ/サンプル/05_オリジナルゲーム制作/スケジュール.xlsx
+++ b/ゲーム科1年/01_後期/ゲームプログラミングⅢ/サンプル/05_オリジナルゲーム制作/スケジュール.xlsx
@@ -5,15 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\ArakiYusuke\Textbook\ゲーム科1年\00_前期\ゲームプログラミングⅢ\サンプル\04_オリジナルゲーム制作\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F13E0B6-A124-41EB-9004-9039D39CBDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453AE08F-E2A1-4290-B89F-B8D8C6511A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4755" yWindow="2070" windowWidth="20175" windowHeight="13410" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="10月" sheetId="6" r:id="rId1"/>
+    <sheet name="11月" sheetId="7" r:id="rId2"/>
+    <sheet name="12月" sheetId="8" r:id="rId3"/>
+    <sheet name="1月" sheetId="9" r:id="rId4"/>
+    <sheet name="2月" sheetId="10" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,17 +41,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
-    <t>Aさん</t>
+    <t>10月</t>
+    <rPh sb="2" eb="3">
+      <t>ガツ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Bさん</t>
+    <t>11月</t>
+    <rPh sb="2" eb="3">
+      <t>ガツ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Cさん</t>
+    <t>冬休み</t>
+    <rPh sb="0" eb="2">
+      <t>フユヤス</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>12月</t>
+    <rPh sb="2" eb="3">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1月</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>β版</t>
+    <rPh sb="1" eb="2">
+      <t>バン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>進捗確認</t>
+    <rPh sb="0" eb="4">
+      <t>シンチョクカクニン</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -58,16 +99,9 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>発表会</t>
+    <t>展示会</t>
     <rPh sb="0" eb="3">
-      <t>ハッピョウカイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>3月</t>
-    <rPh sb="1" eb="2">
-      <t>ガツ</t>
+      <t>テンジカイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -76,7 +110,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,8 +150,16 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -127,6 +169,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -201,7 +249,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -223,20 +271,44 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -551,24 +623,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1593A4E0-6E65-4532-B1F4-86DE2F579452}">
-  <dimension ref="A1:BH6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B441B72D-86AC-4B7F-8676-FD638EE31362}">
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="60" width="2.875" customWidth="1"/>
-    <col min="61" max="87" width="3.125" customWidth="1"/>
+    <col min="2" max="32" width="2.875" customWidth="1"/>
+    <col min="33" max="57" width="3.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:60" s="6" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:32" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3"/>
       <c r="B2" s="4">
         <v>1</v>
@@ -576,10 +645,10 @@
       <c r="C2" s="4">
         <v>2</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="13">
         <v>3</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="13">
         <v>4</v>
       </c>
       <c r="F2" s="4">
@@ -597,31 +666,31 @@
       <c r="J2" s="4">
         <v>9</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="2">
         <v>10</v>
       </c>
       <c r="L2" s="2">
         <v>11</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="2">
         <v>12</v>
       </c>
       <c r="N2" s="5">
         <v>13</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="5">
         <v>14</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="5">
         <v>15</v>
       </c>
       <c r="Q2" s="5">
         <v>16</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="2">
         <v>17</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="2">
         <v>18</v>
       </c>
       <c r="T2" s="5">
@@ -630,19 +699,19 @@
       <c r="U2" s="5">
         <v>20</v>
       </c>
-      <c r="V2" s="2">
+      <c r="V2" s="5">
         <v>21</v>
       </c>
-      <c r="W2" s="2">
+      <c r="W2" s="5">
         <v>22</v>
       </c>
-      <c r="X2" s="2">
+      <c r="X2" s="5">
         <v>23</v>
       </c>
-      <c r="Y2" s="5">
+      <c r="Y2" s="2">
         <v>24</v>
       </c>
-      <c r="Z2" s="5">
+      <c r="Z2" s="2">
         <v>25</v>
       </c>
       <c r="AA2" s="5">
@@ -651,107 +720,21 @@
       <c r="AB2" s="5">
         <v>27</v>
       </c>
-      <c r="AC2" s="2">
+      <c r="AC2" s="5">
         <v>28</v>
       </c>
-      <c r="AD2" s="2">
-        <v>1</v>
+      <c r="AD2" s="5">
+        <v>29</v>
       </c>
       <c r="AE2" s="5">
-        <v>2</v>
-      </c>
-      <c r="AF2" s="5">
-        <v>3</v>
-      </c>
-      <c r="AG2" s="5">
-        <v>4</v>
-      </c>
-      <c r="AH2" s="5">
-        <v>5</v>
-      </c>
-      <c r="AI2" s="5">
-        <v>6</v>
-      </c>
-      <c r="AJ2" s="2">
-        <v>7</v>
-      </c>
-      <c r="AK2" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL2" s="5">
-        <v>9</v>
-      </c>
-      <c r="AM2" s="5">
-        <v>10</v>
-      </c>
-      <c r="AN2" s="5">
-        <v>11</v>
-      </c>
-      <c r="AO2" s="5">
-        <v>12</v>
-      </c>
-      <c r="AP2" s="5">
-        <v>13</v>
-      </c>
-      <c r="AQ2" s="2">
-        <v>14</v>
-      </c>
-      <c r="AR2" s="2">
-        <v>15</v>
-      </c>
-      <c r="AS2" s="5">
-        <v>16</v>
-      </c>
-      <c r="AT2" s="5">
-        <v>17</v>
-      </c>
-      <c r="AU2" s="5">
-        <v>18</v>
-      </c>
-      <c r="AV2" s="5">
-        <v>19</v>
-      </c>
-      <c r="AW2" s="5">
-        <v>20</v>
-      </c>
-      <c r="AX2" s="5">
-        <v>21</v>
-      </c>
-      <c r="AY2" s="5">
-        <v>22</v>
-      </c>
-      <c r="AZ2" s="5">
-        <v>23</v>
-      </c>
-      <c r="BA2" s="5">
-        <v>24</v>
-      </c>
-      <c r="BB2" s="5">
-        <v>25</v>
-      </c>
-      <c r="BC2" s="5">
-        <v>26</v>
-      </c>
-      <c r="BD2" s="5">
-        <v>27</v>
-      </c>
-      <c r="BE2" s="5">
-        <v>28</v>
-      </c>
-      <c r="BF2" s="5">
-        <v>29</v>
-      </c>
-      <c r="BG2" s="5">
         <v>30</v>
       </c>
-      <c r="BH2" s="5">
+      <c r="AF2" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:60" s="10" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="7" t="s">
-        <v>0</v>
-      </c>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -768,7 +751,7 @@
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
+      <c r="R3" s="11"/>
       <c r="S3" s="9"/>
       <c r="T3" s="9"/>
       <c r="U3" s="9"/>
@@ -783,39 +766,9 @@
       <c r="AD3" s="9"/>
       <c r="AE3" s="9"/>
       <c r="AF3" s="9"/>
-      <c r="AG3" s="9"/>
-      <c r="AH3" s="9"/>
-      <c r="AI3" s="9"/>
-      <c r="AJ3" s="9"/>
-      <c r="AK3" s="9"/>
-      <c r="AL3" s="9"/>
-      <c r="AM3" s="9"/>
-      <c r="AN3" s="9"/>
-      <c r="AO3" s="9"/>
-      <c r="AP3" s="9"/>
-      <c r="AQ3" s="9"/>
-      <c r="AR3" s="9"/>
-      <c r="AS3" s="9"/>
-      <c r="AT3" s="9"/>
-      <c r="AU3" s="9"/>
-      <c r="AV3" s="9"/>
-      <c r="AW3" s="9"/>
-      <c r="AX3" s="9"/>
-      <c r="AY3" s="9"/>
-      <c r="AZ3" s="9"/>
-      <c r="BA3" s="9"/>
-      <c r="BB3" s="9"/>
-      <c r="BC3" s="9"/>
-      <c r="BD3" s="9"/>
-      <c r="BE3" s="9"/>
-      <c r="BF3" s="9"/>
-      <c r="BG3" s="9"/>
-      <c r="BH3" s="9"/>
-    </row>
-    <row r="4" spans="1:60" s="10" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="A4" s="7"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -832,7 +785,6 @@
       <c r="O4" s="9"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
       <c r="U4" s="9"/>
@@ -847,39 +799,9 @@
       <c r="AD4" s="9"/>
       <c r="AE4" s="9"/>
       <c r="AF4" s="9"/>
-      <c r="AG4" s="9"/>
-      <c r="AH4" s="9"/>
-      <c r="AI4" s="9"/>
-      <c r="AJ4" s="9"/>
-      <c r="AK4" s="9"/>
-      <c r="AL4" s="9"/>
-      <c r="AM4" s="9"/>
-      <c r="AN4" s="9"/>
-      <c r="AO4" s="9"/>
-      <c r="AP4" s="9"/>
-      <c r="AQ4" s="9"/>
-      <c r="AR4" s="9"/>
-      <c r="AS4" s="9"/>
-      <c r="AT4" s="9"/>
-      <c r="AU4" s="9"/>
-      <c r="AV4" s="9"/>
-      <c r="AW4" s="9"/>
-      <c r="AX4" s="9"/>
-      <c r="AY4" s="9"/>
-      <c r="AZ4" s="9"/>
-      <c r="BA4" s="9"/>
-      <c r="BB4" s="9"/>
-      <c r="BC4" s="9"/>
-      <c r="BD4" s="9"/>
-      <c r="BE4" s="9"/>
-      <c r="BF4" s="9"/>
-      <c r="BG4" s="9"/>
-      <c r="BH4" s="9"/>
-    </row>
-    <row r="5" spans="1:60" s="10" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="7" t="s">
-        <v>2</v>
-      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="A5" s="7"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -911,39 +833,1525 @@
       <c r="AD5" s="9"/>
       <c r="AE5" s="9"/>
       <c r="AF5" s="9"/>
-      <c r="AG5" s="9"/>
-      <c r="AH5" s="9"/>
-      <c r="AI5" s="9"/>
-      <c r="AJ5" s="9"/>
-      <c r="AK5" s="9"/>
-      <c r="AL5" s="9"/>
-      <c r="AM5" s="9"/>
-      <c r="AN5" s="9"/>
-      <c r="AO5" s="9"/>
-      <c r="AP5" s="9"/>
-      <c r="AQ5" s="9"/>
-      <c r="AR5" s="9"/>
-      <c r="AS5" s="9"/>
-      <c r="AT5" s="9"/>
-      <c r="AU5" s="9"/>
-      <c r="AV5" s="9"/>
-      <c r="AW5" s="9"/>
-      <c r="AX5" s="9"/>
-      <c r="AY5" s="9"/>
-      <c r="AZ5" s="9"/>
-      <c r="BA5" s="9"/>
-      <c r="BB5" s="9"/>
-      <c r="BC5" s="9"/>
-      <c r="BD5" s="9"/>
-      <c r="BE5" s="9"/>
-      <c r="BF5" s="9"/>
-      <c r="BG5" s="9"/>
-      <c r="BH5" s="9"/>
-    </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.4">
-      <c r="AV6" s="11" t="s">
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+      <c r="AF6" s="9"/>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="9"/>
+      <c r="AF7" s="9"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="9"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="B9" s="12"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="12"/>
+      <c r="AF9" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{012DFA43-E021-4014-93E9-AF0C73AD4BF2}">
+  <dimension ref="A1:AE9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="31" width="2.875" customWidth="1"/>
+    <col min="32" max="56" width="3.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3"/>
+      <c r="B2" s="13">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13">
+        <v>2</v>
+      </c>
+      <c r="D2" s="13">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4">
         <v>4</v>
       </c>
+      <c r="F2" s="4">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4">
+        <v>6</v>
+      </c>
+      <c r="H2" s="13">
+        <v>7</v>
+      </c>
+      <c r="I2" s="13">
+        <v>8</v>
+      </c>
+      <c r="J2" s="4">
+        <v>9</v>
+      </c>
+      <c r="K2" s="5">
+        <v>10</v>
+      </c>
+      <c r="L2" s="5">
+        <v>11</v>
+      </c>
+      <c r="M2" s="5">
+        <v>12</v>
+      </c>
+      <c r="N2" s="5">
+        <v>13</v>
+      </c>
+      <c r="O2" s="2">
+        <v>14</v>
+      </c>
+      <c r="P2" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>16</v>
+      </c>
+      <c r="R2" s="5">
+        <v>17</v>
+      </c>
+      <c r="S2" s="5">
+        <v>18</v>
+      </c>
+      <c r="T2" s="5">
+        <v>19</v>
+      </c>
+      <c r="U2" s="5">
+        <v>20</v>
+      </c>
+      <c r="V2" s="2">
+        <v>21</v>
+      </c>
+      <c r="W2" s="2">
+        <v>22</v>
+      </c>
+      <c r="X2" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="5">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>25</v>
+      </c>
+      <c r="AA2" s="5">
+        <v>26</v>
+      </c>
+      <c r="AB2" s="5">
+        <v>27</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>28</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>29</v>
+      </c>
+      <c r="AE2" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="9"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="B9" s="12"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C28529B-3F25-4BAF-8EFD-2BE56F93896E}">
+  <dimension ref="A1:AE9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="31" width="2.875" customWidth="1"/>
+    <col min="32" max="56" width="3.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3"/>
+      <c r="B2" s="13">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13">
+        <v>2</v>
+      </c>
+      <c r="D2" s="13">
+        <v>3</v>
+      </c>
+      <c r="E2" s="13">
+        <v>4</v>
+      </c>
+      <c r="F2" s="13">
+        <v>5</v>
+      </c>
+      <c r="G2" s="13">
+        <v>6</v>
+      </c>
+      <c r="H2" s="13">
+        <v>7</v>
+      </c>
+      <c r="I2" s="13">
+        <v>8</v>
+      </c>
+      <c r="J2" s="13">
+        <v>9</v>
+      </c>
+      <c r="K2" s="2">
+        <v>10</v>
+      </c>
+      <c r="L2" s="2">
+        <v>11</v>
+      </c>
+      <c r="M2" s="2">
+        <v>12</v>
+      </c>
+      <c r="N2" s="2">
+        <v>13</v>
+      </c>
+      <c r="O2" s="2">
+        <v>14</v>
+      </c>
+      <c r="P2" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>16</v>
+      </c>
+      <c r="R2" s="2">
+        <v>17</v>
+      </c>
+      <c r="S2" s="2">
+        <v>18</v>
+      </c>
+      <c r="T2" s="2">
+        <v>19</v>
+      </c>
+      <c r="U2" s="2">
+        <v>20</v>
+      </c>
+      <c r="V2" s="2">
+        <v>21</v>
+      </c>
+      <c r="W2" s="2">
+        <v>22</v>
+      </c>
+      <c r="X2" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>25</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>26</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>27</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>28</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>29</v>
+      </c>
+      <c r="AE2" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="9"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="B9" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="15"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29359FC-5D4A-4D3E-B814-DF2396B0EF47}">
+  <dimension ref="A1:AF9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="32" width="2.875" customWidth="1"/>
+    <col min="33" max="56" width="3.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3"/>
+      <c r="B2" s="13">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13">
+        <v>2</v>
+      </c>
+      <c r="D2" s="13">
+        <v>3</v>
+      </c>
+      <c r="E2" s="13">
+        <v>4</v>
+      </c>
+      <c r="F2" s="13">
+        <v>5</v>
+      </c>
+      <c r="G2" s="13">
+        <v>6</v>
+      </c>
+      <c r="H2" s="13">
+        <v>7</v>
+      </c>
+      <c r="I2" s="13">
+        <v>8</v>
+      </c>
+      <c r="J2" s="13">
+        <v>9</v>
+      </c>
+      <c r="K2" s="2">
+        <v>10</v>
+      </c>
+      <c r="L2" s="2">
+        <v>11</v>
+      </c>
+      <c r="M2" s="5">
+        <v>12</v>
+      </c>
+      <c r="N2" s="5">
+        <v>13</v>
+      </c>
+      <c r="O2" s="5">
+        <v>14</v>
+      </c>
+      <c r="P2" s="5">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>16</v>
+      </c>
+      <c r="R2" s="2">
+        <v>17</v>
+      </c>
+      <c r="S2" s="5">
+        <v>18</v>
+      </c>
+      <c r="T2" s="5">
+        <v>19</v>
+      </c>
+      <c r="U2" s="5">
+        <v>20</v>
+      </c>
+      <c r="V2" s="5">
+        <v>21</v>
+      </c>
+      <c r="W2" s="5">
+        <v>22</v>
+      </c>
+      <c r="X2" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>25</v>
+      </c>
+      <c r="AA2" s="5">
+        <v>26</v>
+      </c>
+      <c r="AB2" s="5">
+        <v>27</v>
+      </c>
+      <c r="AC2" s="5">
+        <v>28</v>
+      </c>
+      <c r="AD2" s="5">
+        <v>29</v>
+      </c>
+      <c r="AE2" s="2">
+        <v>30</v>
+      </c>
+      <c r="AF2" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
+      <c r="AF4" s="9"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+      <c r="AF5" s="9"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+      <c r="AF6" s="9"/>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="9"/>
+      <c r="AF7" s="9"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="9"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="B9" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="12"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="12"/>
+      <c r="AE9" s="12"/>
+      <c r="AF9" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E6A191-5A3C-4165-87F1-0277CC85ED5B}">
+  <dimension ref="A1:AK9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="29" width="2.875" customWidth="1"/>
+    <col min="30" max="52" width="3.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3"/>
+      <c r="B2" s="18">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18">
+        <v>2</v>
+      </c>
+      <c r="D2" s="18">
+        <v>3</v>
+      </c>
+      <c r="E2" s="18">
+        <v>4</v>
+      </c>
+      <c r="F2" s="18">
+        <v>5</v>
+      </c>
+      <c r="G2" s="13">
+        <v>6</v>
+      </c>
+      <c r="H2" s="13">
+        <v>7</v>
+      </c>
+      <c r="I2" s="18">
+        <v>8</v>
+      </c>
+      <c r="J2" s="18">
+        <v>9</v>
+      </c>
+      <c r="K2" s="19">
+        <v>10</v>
+      </c>
+      <c r="L2" s="2">
+        <v>11</v>
+      </c>
+      <c r="M2" s="2">
+        <v>12</v>
+      </c>
+      <c r="N2" s="2">
+        <v>13</v>
+      </c>
+      <c r="O2" s="2">
+        <v>14</v>
+      </c>
+      <c r="P2" s="19">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="19">
+        <v>16</v>
+      </c>
+      <c r="R2" s="19">
+        <v>17</v>
+      </c>
+      <c r="S2" s="19">
+        <v>18</v>
+      </c>
+      <c r="T2" s="19">
+        <v>19</v>
+      </c>
+      <c r="U2" s="2">
+        <v>20</v>
+      </c>
+      <c r="V2" s="2">
+        <v>21</v>
+      </c>
+      <c r="W2" s="2">
+        <v>22</v>
+      </c>
+      <c r="X2" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="19">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="19">
+        <v>25</v>
+      </c>
+      <c r="AA2" s="19">
+        <v>26</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>27</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="B9" s="12"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="17"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="16"/>
+      <c r="AJ9" s="16"/>
+      <c r="AK9" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/ゲーム科1年/01_後期/ゲームプログラミングⅢ/サンプル/05_オリジナルゲーム制作/スケジュール.xlsx
+++ b/ゲーム科1年/01_後期/ゲームプログラミングⅢ/サンプル/05_オリジナルゲーム制作/スケジュール.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ArakiYusuke\Textbook\ゲーム科1年\01_後期\ゲームプログラミングⅢ\サンプル\05_オリジナルゲーム制作\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453AE08F-E2A1-4290-B89F-B8D8C6511A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F11F99F-357C-476E-9344-3F79FDE7DD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
   <sheets>
     <sheet name="10月" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>10月</t>
     <rPh sb="2" eb="3">
@@ -102,6 +102,23 @@
     <t>展示会</t>
     <rPh sb="0" eb="3">
       <t>テンジカイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>休校期間</t>
+    <rPh sb="0" eb="2">
+      <t>キュウコウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>休校期間</t>
+    <rPh sb="0" eb="4">
+      <t>キュウコウキカン</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1324,7 +1341,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C28529B-3F25-4BAF-8EFD-2BE56F93896E}">
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1661,6 +1678,18 @@
       <c r="AD9" s="14"/>
       <c r="AE9" s="15"/>
     </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="X10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
+      <c r="AC10" s="17"/>
+      <c r="AD10" s="17"/>
+      <c r="AE10" s="17"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1670,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29359FC-5D4A-4D3E-B814-DF2396B0EF47}">
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -2019,6 +2048,14 @@
       <c r="AE9" s="12"/>
       <c r="AF9" s="12"/>
     </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.4">
+      <c r="B10" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2361,17 +2398,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -2566,6 +2592,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2576,17 +2613,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2605,6 +2631,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
   <ds:schemaRefs>
